--- a/avaliacoes_garantia.xlsx
+++ b/avaliacoes_garantia.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,15 +788,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Excelente produto com pós venda atencioso e competente.</t>
+          <t>Técnico educado e cordial, realizou os reparos necessários, deixando o equipamento em pleno funcionamento.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>45954.47363185186</v>
+        <v>46077.38118149305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+          <t>ODIxYjc4NjQtZDdiOC00MDc2LTk3YzEtNGMwNzU1ZTdkMzkxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Excelente produto com pós venda atencioso e competente.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>45954.47363185186</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Técnico 
 Ótimo relacionamento com o cliente </t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>46043.57604188658</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>NjBmNTZjNjctMjFmYy00ZjU4LTg0NTItZDViMWVlZTE3NDUwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" s="2" t="n">
-        <v>46006.74939984953</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -839,11 +843,11 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" s="2" t="n">
-        <v>45114.58134109954</v>
+        <v>46006.74939984953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
+          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -853,11 +857,11 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" s="2" t="n">
-        <v>46006.64905208333</v>
+        <v>45114.58134109954</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
+          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -867,11 +871,11 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" s="2" t="n">
-        <v>45895.62649680555</v>
+        <v>46006.64905208333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
+          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -879,17 +883,13 @@
       <c r="A29" t="n">
         <v>5</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" s="2" t="n">
-        <v>45954.49367453704</v>
+        <v>45895.62649680555</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
+          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -899,65 +899,69 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
+          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45919.58513085648</v>
+        <v>45954.49367453704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
+          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
+          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>45897.70520351852</v>
+        <v>45919.58513085648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
+          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>45982.55515303241</v>
+        <v>45897.70520351852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
+          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="n">
-        <v>45897.70435114583</v>
+        <v>45982.55515303241</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
+          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -967,11 +971,11 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" s="2" t="n">
-        <v>45940.6359195949</v>
+        <v>45897.70435114583</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
+          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -979,17 +983,13 @@
       <c r="A35" t="n">
         <v>5</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Colaborador muito atencioso. </t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" s="2" t="n">
-        <v>45918.57075675926</v>
+        <v>45940.6359195949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -997,11 +997,29 @@
       <c r="A36" t="n">
         <v>5</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colaborador muito atencioso. </t>
+        </is>
+      </c>
       <c r="C36" s="2" t="n">
+        <v>45918.57075675926</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" s="2" t="n">
         <v>45940.63159275463</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>NzYxOTRkMzgtZDQwNy00ODM5LWI5NDctYzJkMTczZDkzZGQzOjU3MDE2</t>
         </is>

--- a/avaliacoes_garantia.xlsx
+++ b/avaliacoes_garantia.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,15 +595,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tudo solucionado.</t>
+          <t>Muito atencioso e finalmente alguém que entendeu o que precisamos. Espero que agora o ajuste seja feito.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>45982.55324377315</v>
+        <v>46113.45578471065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NTU0NzBmZGUtZTNlZS00OTBkLTlmN2MtZDNhNTM4ZGMyN2NiOjU3MDE2</t>
+          <t>ZDM5ZDM3ZTItMzE3NS00MWNhLTgxZWItZjUzYmNkODkzMDgxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -613,15 +613,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Excelente atendimento!!!</t>
+          <t>Tudo solucionado.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45895.43282017361</v>
+        <v>45982.55324377315</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M2ZkMjljOWYtMmE0NC00YWVhLWI0ODgtODUxMjFjMWI0YmQwOjU3MDE2</t>
+          <t>NTU0NzBmZGUtZTNlZS00OTBkLTlmN2MtZDNhNTM4ZGMyN2NiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -629,13 +629,17 @@
       <c r="A13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Excelente atendimento!!!</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="n">
-        <v>45896.68595259259</v>
+        <v>45895.43282017361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Y2FlMmFjMDMtYmU0ZS00NzQwLTliMmMtOWM2OWUyZTA3NzAzOjU3MDE2</t>
+          <t>M2ZkMjljOWYtMmE0NC00YWVhLWI0ODgtODUxMjFjMWI0YmQwOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -645,11 +649,11 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" s="2" t="n">
-        <v>45919.59230513889</v>
+        <v>45896.68595259259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MDZiY2UyZTQtNDM3Yy00MmY5LTk2NDktMzcwNzU4YWZjZWZlOjU3MDE2</t>
+          <t>Y2FlMmFjMDMtYmU0ZS00NzQwLTliMmMtOWM2OWUyZTA3NzAzOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -659,11 +663,11 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" s="2" t="n">
-        <v>45965.52277326389</v>
+        <v>45919.59230513889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MmJmMjU1YjgtYWExNC00YjFjLTg5NWQtMGYxNGVmNDA2ZDRhOjU3MDE2</t>
+          <t>MDZiY2UyZTQtNDM3Yy00MmY5LTk2NDktMzcwNzU4YWZjZWZlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -673,11 +677,11 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" s="2" t="n">
-        <v>46010.46702450232</v>
+        <v>45965.52277326389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NmNjY2Q0MzYtNWI4ZS00ODk3LTgyZDItNTFkNWMxNWFjYzA5OjU3MDE2</t>
+          <t>MmJmMjU1YjgtYWExNC00YjFjLTg5NWQtMGYxNGVmNDA2ZDRhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -687,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="2" t="n">
-        <v>45951.66084622685</v>
+        <v>46010.46702450232</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MjRkNTkzODMtN2IzMC00N2JhLWI1ZDQtNjYwNDFhNjUxZTU1OjU3MDE2</t>
+          <t>NmNjY2Q0MzYtNWI4ZS00ODk3LTgyZDItNTFkNWMxNWFjYzA5OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -701,11 +705,11 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" s="2" t="n">
-        <v>45919.53137916666</v>
+        <v>45951.66084622685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>YWMxNDdmNmMtMThiZS00MDJmLThmYTEtM2E4MGZlYzY0MTRiOjU3MDE2</t>
+          <t>MjRkNTkzODMtN2IzMC00N2JhLWI1ZDQtNjYwNDFhNjUxZTU1OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -713,17 +717,13 @@
       <c r="A19" t="n">
         <v>5</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Agradecido pelo apoio!!!</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" s="2" t="n">
-        <v>45895.79028740741</v>
+        <v>45919.53137916666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ZDc1MjI5MGQtODAzYy00Y2EzLThlYTktY2ZkOGY5ZmJlNDI5OjU3MDE2</t>
+          <t>YWMxNDdmNmMtMThiZS00MDJmLThmYTEtM2E4MGZlYzY0MTRiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -733,15 +733,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Colaborador bastante atencioso e demonstrou conhecimento do serviço a ser realizado.</t>
+          <t>Agradecido pelo apoio!!!</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46002.57819354167</v>
+        <v>45895.79028740741</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OWQ3MmJiNzktNzkxMy00NDg4LWFjOTItOWRlOWMyOTQ1NmZkOjU3MDE2</t>
+          <t>ZDc1MjI5MGQtODAzYy00Y2EzLThlYTktY2ZkOGY5ZmJlNDI5OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -751,34 +751,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Colaborador bastante atencioso e demonstrou conhecimento do serviço a ser realizado.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46002.57819354167</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OWQ3MmJiNzktNzkxMy00NDg4LWFjOTItOWRlOWMyOTQ1NmZkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t xml:space="preserve">
 Rapaz atencioso e cordial. Obrigado </t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C22" s="2" t="n">
         <v>45926.50978196759</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>ZjZhZGU5MzktZGFiNC00YjdlLTgxN2EtYTkyYWM1ZWE5YjAzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solução rápida e competente </t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>45958.72571003472</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OTcxNWNiMjktMWZhMC00NTg2LWExNmYtYWVlYzAwNDkyMWNlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -788,15 +788,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Técnico educado e cordial, realizou os reparos necessários, deixando o equipamento em pleno funcionamento.</t>
+          <t xml:space="preserve">Solução rápida e competente </t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46077.38118149305</v>
+        <v>45958.72571003472</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ODIxYjc4NjQtZDdiOC00MDc2LTk3YzEtNGMwNzU1ZTdkMzkxOjU3MDE2</t>
+          <t>OTcxNWNiMjktMWZhMC00NTg2LWExNmYtYWVlYzAwNDkyMWNlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -806,15 +806,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Excelente produto com pós venda atencioso e competente.</t>
+          <t>Técnico educado e cordial, realizou os reparos necessários, deixando o equipamento em pleno funcionamento.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>45954.47363185186</v>
+        <v>46077.38118149305</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+          <t>ODIxYjc4NjQtZDdiOC00MDc2LTk3YzEtNGMwNzU1ZTdkMzkxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Excelente produto com pós venda atencioso e competente.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>45954.47363185186</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Técnico 
 Ótimo relacionamento com o cliente </t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>46043.57604188658</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>NjBmNTZjNjctMjFmYy00ZjU4LTg0NTItZDViMWVlZTE3NDUwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" s="2" t="n">
-        <v>46006.74939984953</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -857,11 +861,11 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" s="2" t="n">
-        <v>45114.58134109954</v>
+        <v>46006.74939984953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
+          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -871,11 +875,11 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" s="2" t="n">
-        <v>46006.64905208333</v>
+        <v>45114.58134109954</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
+          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -885,11 +889,11 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" s="2" t="n">
-        <v>45895.62649680555</v>
+        <v>46006.64905208333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
+          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -897,17 +901,13 @@
       <c r="A30" t="n">
         <v>5</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" s="2" t="n">
-        <v>45954.49367453704</v>
+        <v>45895.62649680555</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
+          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -917,65 +917,69 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
+          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>45919.58513085648</v>
+        <v>45954.49367453704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
+          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
+          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>45897.70520351852</v>
+        <v>45919.58513085648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
+          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>45982.55515303241</v>
+        <v>45897.70520351852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
+          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="n">
-        <v>45897.70435114583</v>
+        <v>45982.55515303241</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
+          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -985,11 +989,11 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" s="2" t="n">
-        <v>45940.6359195949</v>
+        <v>45897.70435114583</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
+          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -997,17 +1001,13 @@
       <c r="A36" t="n">
         <v>5</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Colaborador muito atencioso. </t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" s="2" t="n">
-        <v>45918.57075675926</v>
+        <v>45940.6359195949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -1015,11 +1015,29 @@
       <c r="A37" t="n">
         <v>5</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colaborador muito atencioso. </t>
+        </is>
+      </c>
       <c r="C37" s="2" t="n">
+        <v>45918.57075675926</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" s="2" t="n">
         <v>45940.63159275463</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>NzYxOTRkMzgtZDQwNy00ODM5LWI5NDctYzJkMTczZDkzZGQzOjU3MDE2</t>
         </is>

--- a/avaliacoes_garantia.xlsx
+++ b/avaliacoes_garantia.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,11 +460,11 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" s="2" t="n">
-        <v>46034.61868471065</v>
+        <v>46191.97126040509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OWY1NGRiM2EtMjUxMy00YzZjLTg0ZDctMTBhZGU5MjQzZjY2OjU3MDE2</t>
+          <t>OWJjNzgzYmMtYzM1MC00NmZjLTljNGQtNGMxYWUzZjZhMzA0OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -474,43 +474,39 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" s="2" t="n">
-        <v>45898.53136140046</v>
+        <v>46034.61868471065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OGE2MmVlZmEtMGI1YS00M2EzLWFmOTktYWMyMzA3MjVkYjYyOjU3MDE2</t>
+          <t>OWY1NGRiM2EtMjUxMy00YzZjLTg0ZDctMTBhZGU5MjQzZjY2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" s="2" t="n">
-        <v>46001.65142589121</v>
+        <v>45898.53136140046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>YTU1MjU5YTEtYTBkNy00ZDg5LWE5ZDAtN2M1MDIyODc2ZWZhOjU3MDE2</t>
+          <t>OGE2MmVlZmEtMGI1YS00M2EzLWFmOTktYWMyMzA3MjVkYjYyOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Excelente atendimento </t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" s="2" t="n">
-        <v>45905.77066481482</v>
+        <v>46001.65142589121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ODgxNWYzNjgtNjZlYy00YjFiLWFiZGMtZGVkNWIxNGE4ZDY1OjU3MDE2</t>
+          <t>YTU1MjU5YTEtYTBkNy00ZDg5LWE5ZDAtN2M1MDIyODc2ZWZhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -518,13 +514,17 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excelente atendimento </t>
+        </is>
+      </c>
       <c r="C6" s="2" t="n">
-        <v>45912.44327967593</v>
+        <v>45905.77066481482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NjAwYjE5OTAtOGViYy00Y2Q1LWI4MzAtNzhkZTRlNjcxOWJiOjU3MDE2</t>
+          <t>ODgxNWYzNjgtNjZlYy00YjFiLWFiZGMtZGVkNWIxNGE4ZDY1OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -532,32 +532,32 @@
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" s="2" t="n">
+        <v>45912.44327967593</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NjAwYjE5OTAtOGViYy00Y2Q1LWI4MzAtNzhkZTRlNjcxOWJiOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Ele efetuou a limpeza dos locais enferrujados e ensinou como efetuar a limpeza do inox para não riscar .
 Tirou foto dos produtos utilizados para analisar e ficou de dar um retorno.Serviço prestado de acordo.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C8" s="2" t="n">
         <v>45912.71314665509</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Y2Y2NGI4MTktZmVjMi00YWEzLWE0NzctM2JiMDE0YzliZjU5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" s="2" t="n">
-        <v>45986.45500729167</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MzFmMDgzY2ItODY1MC00N2NkLTg1MjctMzhjMzM4NzRkNDNhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -567,11 +567,11 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" s="2" t="n">
-        <v>45902.89908415509</v>
+        <v>45986.45500729167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MzM3NmJjMjQtMTRmMi00NjgxLWI4ZmQtZjJmNjQwMjkxNzhkOjU3MDE2</t>
+          <t>MzFmMDgzY2ItODY1MC00N2NkLTg1MjctMzhjMzM4NzRkNDNhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -581,11 +581,11 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" s="2" t="n">
-        <v>45895.49774995371</v>
+        <v>45902.89908415509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NjM1Zjk4NmEtZjFkNy00MTJiLTkzYmMtNDIwZjFmZmE0ZWIxOjU3MDE2</t>
+          <t>MzM3NmJjMjQtMTRmMi00NjgxLWI4ZmQtZjJmNjQwMjkxNzhkOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -593,17 +593,13 @@
       <c r="A11" t="n">
         <v>5</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Muito atencioso e finalmente alguém que entendeu o que precisamos. Espero que agora o ajuste seja feito.</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" s="2" t="n">
-        <v>46113.45578471065</v>
+        <v>45895.49774995371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ZDM5ZDM3ZTItMzE3NS00MWNhLTgxZWItZjUzYmNkODkzMDgxOjU3MDE2</t>
+          <t>NjM1Zjk4NmEtZjFkNy00MTJiLTkzYmMtNDIwZjFmZmE0ZWIxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -613,15 +609,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tudo solucionado.</t>
+          <t>Muito atencioso e finalmente alguém que entendeu o que precisamos. Espero que agora o ajuste seja feito.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45982.55324377315</v>
+        <v>46113.45578471065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NTU0NzBmZGUtZTNlZS00OTBkLTlmN2MtZDNhNTM4ZGMyN2NiOjU3MDE2</t>
+          <t>ZDM5ZDM3ZTItMzE3NS00MWNhLTgxZWItZjUzYmNkODkzMDgxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -631,15 +627,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Excelente atendimento!!!</t>
+          <t>Tudo solucionado.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>45895.43282017361</v>
+        <v>45982.55324377315</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M2ZkMjljOWYtMmE0NC00YWVhLWI0ODgtODUxMjFjMWI0YmQwOjU3MDE2</t>
+          <t>NTU0NzBmZGUtZTNlZS00OTBkLTlmN2MtZDNhNTM4ZGMyN2NiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -647,13 +643,17 @@
       <c r="A14" t="n">
         <v>5</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Excelente atendimento!!!</t>
+        </is>
+      </c>
       <c r="C14" s="2" t="n">
-        <v>45896.68595259259</v>
+        <v>45895.43282017361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Y2FlMmFjMDMtYmU0ZS00NzQwLTliMmMtOWM2OWUyZTA3NzAzOjU3MDE2</t>
+          <t>M2ZkMjljOWYtMmE0NC00YWVhLWI0ODgtODUxMjFjMWI0YmQwOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -663,11 +663,11 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" s="2" t="n">
-        <v>45919.59230513889</v>
+        <v>45896.68595259259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MDZiY2UyZTQtNDM3Yy00MmY5LTk2NDktMzcwNzU4YWZjZWZlOjU3MDE2</t>
+          <t>Y2FlMmFjMDMtYmU0ZS00NzQwLTliMmMtOWM2OWUyZTA3NzAzOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -677,11 +677,11 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" s="2" t="n">
-        <v>45965.52277326389</v>
+        <v>45919.59230513889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MmJmMjU1YjgtYWExNC00YjFjLTg5NWQtMGYxNGVmNDA2ZDRhOjU3MDE2</t>
+          <t>MDZiY2UyZTQtNDM3Yy00MmY5LTk2NDktMzcwNzU4YWZjZWZlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="2" t="n">
-        <v>46010.46702450232</v>
+        <v>45965.52277326389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NmNjY2Q0MzYtNWI4ZS00ODk3LTgyZDItNTFkNWMxNWFjYzA5OjU3MDE2</t>
+          <t>MmJmMjU1YjgtYWExNC00YjFjLTg5NWQtMGYxNGVmNDA2ZDRhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -705,11 +705,11 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" s="2" t="n">
-        <v>45951.66084622685</v>
+        <v>46010.46702450232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MjRkNTkzODMtN2IzMC00N2JhLWI1ZDQtNjYwNDFhNjUxZTU1OjU3MDE2</t>
+          <t>NmNjY2Q0MzYtNWI4ZS00ODk3LTgyZDItNTFkNWMxNWFjYzA5OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -719,11 +719,11 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" s="2" t="n">
-        <v>45919.53137916666</v>
+        <v>45951.66084622685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>YWMxNDdmNmMtMThiZS00MDJmLThmYTEtM2E4MGZlYzY0MTRiOjU3MDE2</t>
+          <t>MjRkNTkzODMtN2IzMC00N2JhLWI1ZDQtNjYwNDFhNjUxZTU1OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -731,17 +731,13 @@
       <c r="A20" t="n">
         <v>5</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Agradecido pelo apoio!!!</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" s="2" t="n">
-        <v>45895.79028740741</v>
+        <v>45919.53137916666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ZDc1MjI5MGQtODAzYy00Y2EzLThlYTktY2ZkOGY5ZmJlNDI5OjU3MDE2</t>
+          <t>YWMxNDdmNmMtMThiZS00MDJmLThmYTEtM2E4MGZlYzY0MTRiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -751,15 +747,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Colaborador bastante atencioso e demonstrou conhecimento do serviço a ser realizado.</t>
+          <t>Agradecido pelo apoio!!!</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46002.57819354167</v>
+        <v>45895.79028740741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OWQ3MmJiNzktNzkxMy00NDg4LWFjOTItOWRlOWMyOTQ1NmZkOjU3MDE2</t>
+          <t>ZDc1MjI5MGQtODAzYy00Y2EzLThlYTktY2ZkOGY5ZmJlNDI5OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -769,34 +765,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Colaborador bastante atencioso e demonstrou conhecimento do serviço a ser realizado.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46002.57819354167</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OWQ3MmJiNzktNzkxMy00NDg4LWFjOTItOWRlOWMyOTQ1NmZkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t xml:space="preserve">
 Rapaz atencioso e cordial. Obrigado </t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C23" s="2" t="n">
         <v>45926.50978196759</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>ZjZhZGU5MzktZGFiNC00YjdlLTgxN2EtYTkyYWM1ZWE5YjAzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solução rápida e competente </t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>45958.72571003472</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>OTcxNWNiMjktMWZhMC00NTg2LWExNmYtYWVlYzAwNDkyMWNlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -806,15 +802,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Técnico educado e cordial, realizou os reparos necessários, deixando o equipamento em pleno funcionamento.</t>
+          <t xml:space="preserve">Solução rápida e competente </t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46077.38118149305</v>
+        <v>45958.72571003472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ODIxYjc4NjQtZDdiOC00MDc2LTk3YzEtNGMwNzU1ZTdkMzkxOjU3MDE2</t>
+          <t>OTcxNWNiMjktMWZhMC00NTg2LWExNmYtYWVlYzAwNDkyMWNlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -824,15 +820,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Excelente produto com pós venda atencioso e competente.</t>
+          <t>Técnico educado e cordial, realizou os reparos necessários, deixando o equipamento em pleno funcionamento.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>45954.47363185186</v>
+        <v>46077.38118149305</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+          <t>ODIxYjc4NjQtZDdiOC00MDc2LTk3YzEtNGMwNzU1ZTdkMzkxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -842,30 +838,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Excelente produto com pós venda atencioso e competente.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>45954.47363185186</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Técnico 
 Ótimo relacionamento com o cliente </t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C27" s="2" t="n">
         <v>46043.57604188658</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>NjBmNTZjNjctMjFmYy00ZjU4LTg0NTItZDViMWVlZTE3NDUwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" s="2" t="n">
-        <v>46006.74939984953</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -875,11 +875,11 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" s="2" t="n">
-        <v>45114.58134109954</v>
+        <v>46006.74939984953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
+          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -889,11 +889,11 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" s="2" t="n">
-        <v>46006.64905208333</v>
+        <v>45114.58134109954</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
+          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -903,11 +903,11 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" s="2" t="n">
-        <v>45895.62649680555</v>
+        <v>46006.64905208333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
+          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -915,17 +915,13 @@
       <c r="A31" t="n">
         <v>5</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" s="2" t="n">
-        <v>45954.49367453704</v>
+        <v>45895.62649680555</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
+          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -935,65 +931,69 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
+          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>45919.58513085648</v>
+        <v>45954.49367453704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
+          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
+          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>45897.70520351852</v>
+        <v>45919.58513085648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
+          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>45982.55515303241</v>
+        <v>45897.70520351852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
+          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="n">
-        <v>45897.70435114583</v>
+        <v>45982.55515303241</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
+          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" s="2" t="n">
-        <v>45940.6359195949</v>
+        <v>45897.70435114583</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
+          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -1015,17 +1015,13 @@
       <c r="A37" t="n">
         <v>5</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Colaborador muito atencioso. </t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" s="2" t="n">
-        <v>45918.57075675926</v>
+        <v>45940.6359195949</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -1033,11 +1029,29 @@
       <c r="A38" t="n">
         <v>5</v>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colaborador muito atencioso. </t>
+        </is>
+      </c>
       <c r="C38" s="2" t="n">
+        <v>45918.57075675926</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" s="2" t="n">
         <v>45940.63159275463</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>NzYxOTRkMzgtZDQwNy00ODM5LWI5NDctYzJkMTczZDkzZGQzOjU3MDE2</t>
         </is>

--- a/avaliacoes_garantia.xlsx
+++ b/avaliacoes_garantia.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,11 +460,11 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" s="2" t="n">
-        <v>46191.97126040509</v>
+        <v>46210.55709944444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OWJjNzgzYmMtYzM1MC00NmZjLTljNGQtNGMxYWUzZjZhMzA0OjU3MDE2</t>
+          <t>YzIyYTViNzUtYTljMy00NGEzLWI2NmMtMDBmYzQzOTNhNjc2OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -474,11 +474,11 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" s="2" t="n">
-        <v>46034.61868471065</v>
+        <v>46191.97126040509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OWY1NGRiM2EtMjUxMy00YzZjLTg0ZDctMTBhZGU5MjQzZjY2OjU3MDE2</t>
+          <t>OWJjNzgzYmMtYzM1MC00NmZjLTljNGQtNGMxYWUzZjZhMzA0OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -488,43 +488,39 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" s="2" t="n">
-        <v>45898.53136140046</v>
+        <v>46034.61868471065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OGE2MmVlZmEtMGI1YS00M2EzLWFmOTktYWMyMzA3MjVkYjYyOjU3MDE2</t>
+          <t>OWY1NGRiM2EtMjUxMy00YzZjLTg0ZDctMTBhZGU5MjQzZjY2OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" s="2" t="n">
-        <v>46001.65142589121</v>
+        <v>45898.53136140046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YTU1MjU5YTEtYTBkNy00ZDg5LWE5ZDAtN2M1MDIyODc2ZWZhOjU3MDE2</t>
+          <t>OGE2MmVlZmEtMGI1YS00M2EzLWFmOTktYWMyMzA3MjVkYjYyOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Excelente atendimento </t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" s="2" t="n">
-        <v>45905.77066481482</v>
+        <v>46001.65142589121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ODgxNWYzNjgtNjZlYy00YjFiLWFiZGMtZGVkNWIxNGE4ZDY1OjU3MDE2</t>
+          <t>YTU1MjU5YTEtYTBkNy00ZDg5LWE5ZDAtN2M1MDIyODc2ZWZhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -532,13 +528,17 @@
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excelente atendimento </t>
+        </is>
+      </c>
       <c r="C7" s="2" t="n">
-        <v>45912.44327967593</v>
+        <v>45905.77066481482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NjAwYjE5OTAtOGViYy00Y2Q1LWI4MzAtNzhkZTRlNjcxOWJiOjU3MDE2</t>
+          <t>ODgxNWYzNjgtNjZlYy00YjFiLWFiZGMtZGVkNWIxNGE4ZDY1OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -546,46 +546,46 @@
       <c r="A8" t="n">
         <v>5</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" s="2" t="n">
+        <v>45912.44327967593</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NjAwYjE5OTAtOGViYy00Y2Q1LWI4MzAtNzhkZTRlNjcxOWJiOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" s="2" t="n">
+        <v>46210.60664523148</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MWFmNTdlNTEtMjFkYS00MWM3LWE0NTUtODU4Y2YxZWMzYmM0OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Ele efetuou a limpeza dos locais enferrujados e ensinou como efetuar a limpeza do inox para não riscar .
 Tirou foto dos produtos utilizados para analisar e ficou de dar um retorno.Serviço prestado de acordo.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C10" s="2" t="n">
         <v>45912.71314665509</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Y2Y2NGI4MTktZmVjMi00YWEzLWE0NzctM2JiMDE0YzliZjU5OjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" s="2" t="n">
-        <v>45986.45500729167</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MzFmMDgzY2ItODY1MC00N2NkLTg1MjctMzhjMzM4NzRkNDNhOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" s="2" t="n">
-        <v>45902.89908415509</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MzM3NmJjMjQtMTRmMi00NjgxLWI4ZmQtZjJmNjQwMjkxNzhkOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -595,11 +595,11 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" s="2" t="n">
-        <v>45895.49774995371</v>
+        <v>45986.45500729167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NjM1Zjk4NmEtZjFkNy00MTJiLTkzYmMtNDIwZjFmZmE0ZWIxOjU3MDE2</t>
+          <t>MzFmMDgzY2ItODY1MC00N2NkLTg1MjctMzhjMzM4NzRkNDNhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,13 @@
       <c r="A12" t="n">
         <v>5</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Muito atencioso e finalmente alguém que entendeu o que precisamos. Espero que agora o ajuste seja feito.</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" s="2" t="n">
-        <v>46113.45578471065</v>
+        <v>45902.89908415509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ZDM5ZDM3ZTItMzE3NS00MWNhLTgxZWItZjUzYmNkODkzMDgxOjU3MDE2</t>
+          <t>MzM3NmJjMjQtMTRmMi00NjgxLWI4ZmQtZjJmNjQwMjkxNzhkOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -625,17 +621,13 @@
       <c r="A13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Tudo solucionado.</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" s="2" t="n">
-        <v>45982.55324377315</v>
+        <v>45895.49774995371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NTU0NzBmZGUtZTNlZS00OTBkLTlmN2MtZDNhNTM4ZGMyN2NiOjU3MDE2</t>
+          <t>NjM1Zjk4NmEtZjFkNy00MTJiLTkzYmMtNDIwZjFmZmE0ZWIxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -645,15 +637,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Excelente atendimento!!!</t>
+          <t>Muito atencioso e finalmente alguém que entendeu o que precisamos. Espero que agora o ajuste seja feito.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>45895.43282017361</v>
+        <v>46113.45578471065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M2ZkMjljOWYtMmE0NC00YWVhLWI0ODgtODUxMjFjMWI0YmQwOjU3MDE2</t>
+          <t>ZDM5ZDM3ZTItMzE3NS00MWNhLTgxZWItZjUzYmNkODkzMDgxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -661,13 +653,17 @@
       <c r="A15" t="n">
         <v>5</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tudo solucionado.</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="n">
-        <v>45896.68595259259</v>
+        <v>45982.55324377315</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Y2FlMmFjMDMtYmU0ZS00NzQwLTliMmMtOWM2OWUyZTA3NzAzOjU3MDE2</t>
+          <t>NTU0NzBmZGUtZTNlZS00OTBkLTlmN2MtZDNhNTM4ZGMyN2NiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -675,13 +671,17 @@
       <c r="A16" t="n">
         <v>5</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Excelente atendimento!!!</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="n">
-        <v>45919.59230513889</v>
+        <v>45895.43282017361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MDZiY2UyZTQtNDM3Yy00MmY5LTk2NDktMzcwNzU4YWZjZWZlOjU3MDE2</t>
+          <t>M2ZkMjljOWYtMmE0NC00YWVhLWI0ODgtODUxMjFjMWI0YmQwOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -691,11 +691,11 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="2" t="n">
-        <v>45965.52277326389</v>
+        <v>45896.68595259259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MmJmMjU1YjgtYWExNC00YjFjLTg5NWQtMGYxNGVmNDA2ZDRhOjU3MDE2</t>
+          <t>Y2FlMmFjMDMtYmU0ZS00NzQwLTliMmMtOWM2OWUyZTA3NzAzOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -705,11 +705,11 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" s="2" t="n">
-        <v>46010.46702450232</v>
+        <v>45919.59230513889</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NmNjY2Q0MzYtNWI4ZS00ODk3LTgyZDItNTFkNWMxNWFjYzA5OjU3MDE2</t>
+          <t>MDZiY2UyZTQtNDM3Yy00MmY5LTk2NDktMzcwNzU4YWZjZWZlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -719,11 +719,11 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" s="2" t="n">
-        <v>45951.66084622685</v>
+        <v>45965.52277326389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MjRkNTkzODMtN2IzMC00N2JhLWI1ZDQtNjYwNDFhNjUxZTU1OjU3MDE2</t>
+          <t>MmJmMjU1YjgtYWExNC00YjFjLTg5NWQtMGYxNGVmNDA2ZDRhOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -733,11 +733,11 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" s="2" t="n">
-        <v>45919.53137916666</v>
+        <v>46010.46702450232</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>YWMxNDdmNmMtMThiZS00MDJmLThmYTEtM2E4MGZlYzY0MTRiOjU3MDE2</t>
+          <t>NmNjY2Q0MzYtNWI4ZS00ODk3LTgyZDItNTFkNWMxNWFjYzA5OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,13 @@
       <c r="A21" t="n">
         <v>5</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Agradecido pelo apoio!!!</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" s="2" t="n">
-        <v>45895.79028740741</v>
+        <v>45951.66084622685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ZDc1MjI5MGQtODAzYy00Y2EzLThlYTktY2ZkOGY5ZmJlNDI5OjU3MDE2</t>
+          <t>MjRkNTkzODMtN2IzMC00N2JhLWI1ZDQtNjYwNDFhNjUxZTU1OjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -763,17 +759,13 @@
       <c r="A22" t="n">
         <v>5</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Colaborador bastante atencioso e demonstrou conhecimento do serviço a ser realizado.</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" s="2" t="n">
-        <v>46002.57819354167</v>
+        <v>45919.53137916666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OWQ3MmJiNzktNzkxMy00NDg4LWFjOTItOWRlOWMyOTQ1NmZkOjU3MDE2</t>
+          <t>YWMxNDdmNmMtMThiZS00MDJmLThmYTEtM2E4MGZlYzY0MTRiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -783,52 +775,52 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Agradecido pelo apoio!!!</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>45895.79028740741</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ZDc1MjI5MGQtODAzYy00Y2EzLThlYTktY2ZkOGY5ZmJlNDI5OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Colaborador bastante atencioso e demonstrou conhecimento do serviço a ser realizado.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46002.57819354167</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OWQ3MmJiNzktNzkxMy00NDg4LWFjOTItOWRlOWMyOTQ1NmZkOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t xml:space="preserve">
 Rapaz atencioso e cordial. Obrigado </t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C25" s="2" t="n">
         <v>45926.50978196759</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>ZjZhZGU5MzktZGFiNC00YjdlLTgxN2EtYTkyYWM1ZWE5YjAzOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solução rápida e competente </t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>45958.72571003472</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>OTcxNWNiMjktMWZhMC00NTg2LWExNmYtYWVlYzAwNDkyMWNlOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Técnico educado e cordial, realizou os reparos necessários, deixando o equipamento em pleno funcionamento.</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>46077.38118149305</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ODIxYjc4NjQtZDdiOC00MDc2LTk3YzEtNGMwNzU1ZTdkMzkxOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -838,15 +830,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Excelente produto com pós venda atencioso e competente.</t>
+          <t xml:space="preserve">Solução rápida e competente </t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>45954.47363185186</v>
+        <v>45958.72571003472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+          <t>OTcxNWNiMjktMWZhMC00NTg2LWExNmYtYWVlYzAwNDkyMWNlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -856,44 +848,52 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Técnico educado e cordial, realizou os reparos necessários, deixando o equipamento em pleno funcionamento.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46077.38118149305</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ODIxYjc4NjQtZDdiOC00MDc2LTk3YzEtNGMwNzU1ZTdkMzkxOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Excelente produto com pós venda atencioso e competente.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>45954.47363185186</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ZDhlNGM1NDAtZWMwMy00OGRlLWE0ZDktM2JlODM0YzJhMWYwOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Técnico 
 Ótimo relacionamento com o cliente </t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C29" s="2" t="n">
         <v>46043.57604188658</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>NjBmNTZjNjctMjFmYy00ZjU4LTg0NTItZDViMWVlZTE3NDUwOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" s="2" t="n">
-        <v>46006.74939984953</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" s="2" t="n">
-        <v>45114.58134109954</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -903,11 +903,11 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" s="2" t="n">
-        <v>46006.64905208333</v>
+        <v>46006.74939984953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
+          <t>ZmYzMjBkNWUtOWQ5YS00MDFiLTk2NmItZTBlMGFlNjE3YmZiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -917,11 +917,11 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" s="2" t="n">
-        <v>45895.62649680555</v>
+        <v>45114.58134109954</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
+          <t>MzA4YThhOWQtYjY4NS00MGZmLWE1NWItNjEwMDM4N2M1MjFiOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,13 @@
       <c r="A32" t="n">
         <v>5</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" s="2" t="n">
-        <v>45954.49367453704</v>
+        <v>46006.64905208333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
+          <t>YmIzNjc4MmUtMjk5Mi00NTY3LWE5ZTEtY2VkYTU4MWM3N2NlOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -947,81 +943,85 @@
       <c r="A33" t="n">
         <v>5</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" s="2" t="n">
-        <v>45919.58513085648</v>
+        <v>45895.62649680555</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
+          <t>NjMzNDFkZTQtNWEwYi00MGVhLWE0YTMtZDEzMmM1YjFjNmUyOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
+          <t>O equipamento agora está funcionando perfeitamente. Ainda não testamos para a esterilização do nosso produto. Mas acredito que vai da tudo certo.</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>45897.70520351852</v>
+        <v>45954.49367453704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
+          <t>ZjIwMzgwNmItMDdmNy00OWM3LWIxMzEtYTVhZjkwNDM0OGQzOjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+          <t xml:space="preserve">Parece que vocês estão dando um rumo melhor no atendimento </t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>45982.55515303241</v>
+        <v>45919.58513085648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
+          <t>NzA2MGY5NmYtZmUwZi00NTc2LTlmMDAtZjMzM2NjYzJmYWI1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelo q.acompanhei ele fez o serviço mas uma das geladeiras continua sem baixar a temperatura ela chega no mínimo 10 graus </t>
+        </is>
+      </c>
       <c r="C36" s="2" t="n">
-        <v>45897.70435114583</v>
+        <v>45897.70520351852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
+          <t>ZjJlMGMyZjMtOWY2Yy00Yzc4LTllZmItMGM5MDE5ZjRjZmU1OjU3MDE2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5</v>
-      </c>
-      <c r="B37" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>O colaborador Julio Francisco fez deu aperto em uma braçadeira que estava solta além de colocar um novo parafuso, porém não trocou a gaxeta da porta pois o arrebite é diferente</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="n">
-        <v>45940.6359195949</v>
+        <v>45982.55515303241</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
+          <t>OTc0ZmNmYTQtZTVjNi00MWQzLWI4OTQtNDI4YjYxYzcxMDRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,13 @@
       <c r="A38" t="n">
         <v>5</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Colaborador muito atencioso. </t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" s="2" t="n">
-        <v>45918.57075675926</v>
+        <v>45897.70435114583</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+          <t>ZGZmYTBjMjEtN2ZiOC00NTUzLTg2NDEtODg4ZWJlNTI2ZWRjOjU3MDE2</t>
         </is>
       </c>
     </row>
@@ -1049,9 +1045,41 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" s="2" t="n">
+        <v>45940.6359195949</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ZDljNWUxNGUtNDI1OS00ZTZhLWEzZmMtODlmMmZkMzNlMzBjOjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colaborador muito atencioso. </t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>45918.57075675926</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Yzg4MTJkNjgtYzBhOS00ODY0LWE3NmItMjMzN2ZkMWUwODA2OjU3MDE2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" s="2" t="n">
         <v>45940.63159275463</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>NzYxOTRkMzgtZDQwNy00ODM5LWI5NDctYzJkMTczZDkzZGQzOjU3MDE2</t>
         </is>
